--- a/RSL/suplementos/matriz_extraccion.xlsx
+++ b/RSL/suplementos/matriz_extraccion.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>registros reales de incidentes</t>
+          <t>benchmark anotado de terceros</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
     </row>
@@ -20961,7 +20961,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
     </row>
